--- a/public/examples/import_complet_exemple.xlsx
+++ b/public/examples/import_complet_exemple.xlsx
@@ -648,7 +648,7 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>12345678901234</v>
+        <v>55566677788899</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -666,7 +666,7 @@
         <v>17</v>
       </c>
       <c r="H2">
-        <v>12345678901234</v>
+        <v>55566677788899</v>
       </c>
       <c r="I2" t="s">
         <v>18</v>
@@ -686,7 +686,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>98765432109876</v>
+        <v>99988877766655</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
@@ -704,7 +704,7 @@
         <v>27</v>
       </c>
       <c r="H3">
-        <v>98765432109876</v>
+        <v>99988877766655</v>
       </c>
       <c r="I3" t="s">
         <v>28</v>
@@ -724,7 +724,7 @@
         <v>32</v>
       </c>
       <c r="B4">
-        <v>11122233344455</v>
+        <v>44433322211100</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
@@ -742,7 +742,7 @@
         <v>37</v>
       </c>
       <c r="H4">
-        <v>11122233344455</v>
+        <v>44433322211100</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
